--- a/OUTPUT/direct_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/OUTPUT/direct_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.0001999200319872051</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6577369052379048</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.669</v>
+        <v>0.6689324270291883</v>
       </c>
     </row>
   </sheetData>
